--- a/bulk-errors/failed-1.xlsx
+++ b/bulk-errors/failed-1.xlsx
@@ -70,7 +70,7 @@
     <t>Sumit</t>
   </si>
   <si>
-    <t>3/3/01</t>
+    <t>03-03-2001</t>
   </si>
   <si>
     <t>LMN School</t>
@@ -103,7 +103,7 @@
     <t>Suresh</t>
   </si>
   <si>
-    <t>10/10/00</t>
+    <t>10-10-2000</t>
   </si>
   <si>
     <t>MNO School</t>
@@ -115,7 +115,7 @@
     <t>B</t>
   </si>
   <si>
-    <t>1/1/00</t>
+    <t>01-01-2000</t>
   </si>
   <si>
     <t>XYZ</t>
